--- a/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.4-rescored.xlsx
+++ b/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.4-rescored.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="Re212a3ad125d4ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="R9186be85021947b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3322,7 +3322,7 @@
         <x:v>0.912676</x:v>
       </x:c>
       <x:c r="E56" s="23" t="n">
-        <x:v>0.8606945680337507</x:v>
+        <x:v>0.8771860119857112</x:v>
       </x:c>
       <x:c r="F56" s="23" t="str">
         <x:v>平均分</x:v>
@@ -3331,7 +3331,7 @@
         <x:v>0.915456</x:v>
       </x:c>
       <x:c r="H56" s="23" t="n">
-        <x:v>0.8825376152069491</x:v>
+        <x:v>0.8951846740304784</x:v>
       </x:c>
       <x:c r="I56" s="23" t="str">
         <x:v>平均分</x:v>
@@ -3340,7 +3340,7 @@
         <x:v>0.906391</x:v>
       </x:c>
       <x:c r="K56" s="23" t="n">
-        <x:v>0.8647874743370195</x:v>
+        <x:v>0.8728266900232937</x:v>
       </x:c>
       <x:c r="L56" s="23" t="str">
         <x:v>平均分</x:v>
@@ -3349,11 +3349,11 @@
         <x:v>0.898382</x:v>
       </x:c>
       <x:c r="N56" s="60" t="n">
-        <x:v>0.8619780245298304</x:v>
+        <x:v>0.8670760637455168</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R489d78d6c9734708"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbb0b891f35240c6"/>
 </x:worksheet>
 </file>